--- a/docs/reports/Test_Cases_Manual_Dispatch_Batch_and_Multi_Order_Driver.xlsx
+++ b/docs/reports/Test_Cases_Manual_Dispatch_Batch_and_Multi_Order_Driver.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dispatch Batch &amp; Multi-Order" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dispatch Batch &amp; Multi-Order'!$A$1:$J$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dispatch Batch &amp; Multi-Order'!$A$1:$J$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -50,7 +50,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="000F172A"/>
         <bgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,25 +108,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -134,8 +125,20 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -502,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,7 +568,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Catatan Verifikasi</t>
+          <t>Catatan Verifikasi / Defect Note</t>
         </is>
       </c>
     </row>
@@ -619,7 +622,7 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -666,14 +669,14 @@
           <t>HTTP 200 OK diterima, banner hijau 'Pengaturan tersimpan.' muncul di UI.</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="J3" s="10" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -727,7 +730,7 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -773,14 +776,14 @@
           <t>Nilai 0 tersimpan valid, menandakan tawaran batch tidak akan auto-expired.</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -834,7 +837,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -881,14 +884,14 @@
           <t>Daftar band lama berhasil digantikan oleh konfigurasi baru sesuai aturan bisnis.</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="J7" s="10" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -941,7 +944,7 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -987,14 +990,14 @@
           <t>Nilai desimal diformat dan disimpan presisi tanpa pembulatan liar.</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="J9" s="10" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1050,7 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -1093,14 +1096,14 @@
           <t>Server menolak dengan HTTP 422: 'Ukuran batch harus bilangan bulat 1 sampai 50.'</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1156,7 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -1198,14 +1201,14 @@
           <t>Akses diblokir dan dialihkan aman ke halaman /login (HTTP 302/401).</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1260,7 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -1302,14 +1305,14 @@
           <t>Seluruh request diproses konsisten tanpa memicu error internal server 500.</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1365,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -1408,14 +1411,14 @@
           <t>Konfigurasi Staging 100% pulih sempurna untuk kelangsungan ekosistem tim QA.</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1471,7 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -1514,14 +1517,14 @@
           <t>Terkonfirmasi 100% TIDAK ADA countdown timer/detik mundur pada tawaran order.</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="J19" s="10" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1577,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -1619,14 +1622,14 @@
           <t>Badge 'Pesanan Reguler' dan 'Advance Booking' tampil berbeda secara tegas.</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="J21" s="10" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1681,7 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -1723,14 +1726,14 @@
           <t>Tawaran tidak hilang secara sepihak dan tetap dapat diambil oleh driver.</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1785,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -1827,14 +1830,14 @@
           <t>Order dikeluarkan dari layar driver; order batch lainnya tetap utuh dan aktif.</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1890,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -1933,14 +1936,14 @@
           <t>Driver A menerima notifikasi valid: 'Orderan sudah diambil oleh pengemudi lain'.</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -1992,7 +1995,7 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -2037,14 +2040,14 @@
           <t>Sistem menerapkan atomic lock; hanya request pertama diproses tanpa duplikasi.</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="J29" s="10" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2099,7 @@
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -2142,14 +2145,14 @@
           <t>Daftar pesanan tetap sinkron dan aplikasi tidak mengalami reset state liar.</t>
         </is>
       </c>
-      <c r="I31" s="11" t="inlineStr">
+      <c r="I31" s="6" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="J31" s="10" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2205,7 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -2248,14 +2251,14 @@
           <t>15 pesanan termuat utuh tanpa countdown timer, memory footprint stabil.</t>
         </is>
       </c>
-      <c r="I33" s="11" t="inlineStr">
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="J33" s="10" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2310,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -2353,14 +2356,14 @@
           <t>Order ke-7 aktif ke trip driver; 9 order lainnya tetap standby di penawaran.</t>
         </is>
       </c>
-      <c r="I35" s="11" t="inlineStr">
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="J35" s="10" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2415,7 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -2457,14 +2460,14 @@
           <t>Titik potong KM ditangani deterministik sesuai spesifikasi interval PRD.</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr">
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="J37" s="10" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2519,7 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -2562,14 +2565,14 @@
           <t>Sistem menangani pesanan di luar jangkauan secara aman tanpa crash atau panic error.</t>
         </is>
       </c>
-      <c r="I39" s="11" t="inlineStr">
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2627,7 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
@@ -2641,48 +2644,908 @@
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
+          <t>Pilar 4: Negative False</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>P0 (Critical)</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>Alur Pembatalan Pasca-Terima Pulih Kembali ke Pool Tanpa Mematikan Order</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>Driver telah menerima pesanan batch ORD-E2E-CANCEL-01</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>1. Driver ajukan pembatalan dengan alasan 'Kendala Kendaraan Driver'.
+2. Sistem verifikasi pelepasan pesanan.
+3. Amati status order di customer dan ketersediaan untuk driver lain.</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>Order TIDAK DIBATALKAN ke customer; status beralih ke RE_DISPATCHING, driver pemohon di-blacklist, dan order di-reassign ke sisa rekanan pool.</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="54" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>TC-CASCADE-PT-01</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Multi-Driver Cascade</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Pilar 1: Positive True</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>P0 (Critical)</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Siaran Simultan 5 Driver Ring 1 &amp; Instant Popup Revocation saat Diambil</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Customer membuat order reguler baru. 5 Driver standby di Ring 1 (&lt; 5 KM), 2 Driver di Ring 2 (&gt; 5 KM).</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>1. Sistem broadcast order ke seluruh 5 driver Ring 1 secara bersamaan.
+2. Verifikasi seluruh 5 driver menerima popup order.
+3. Driver 3 (DRV-03) melakukan Swipe Terima order.
+4. Amati layar 4 driver rekanan lainnya di Ring 1.</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Kelima driver menerima popup serentak. Saat DRV-03 menerima, popup di DRV-01, DRV-02, DRV-04, dan DRV-05 SEKETIKA DICABUT (LENYAP TANPA BEKAS).</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="54" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>TC-CASCADE-PT-02</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Multi-Driver Cascade</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Pilar 1: Positive True</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>P0 (Critical)</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>Advance Booking Cascading &amp; Instant Revocation Matriks Jarak Khusus</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>Customer membuat pesanan terjadwal (Advance Booking, 8.5 KM, Rp 65.000).</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>1. Sistem mendispatch batch Advance Booking ke Ring 1.
+2. Driver 1 melakukan Swipe Terima pada pesanan Advance Booking.
+3. Amati layar driver rekanan.</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>Badge dan parameter Advance Booking terpisah rapi. Popup seketika dicabut dari rekanan begitu Driver 1 menerima, jadwal tersinkronisasi presisi.</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="54" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>TC-CASCADE-PF-01</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Multi-Driver Cascade</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Pilar 2: Positive False</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>P0 (Critical)</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Driver Reject Memicu Re-dispatch ke Rekan &amp; Blacklist Exclusion Penolak</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>5 Driver Ring 1 menerima broadcast order yang sama secara bersamaan.</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>1. Driver 1 menekan tombol 'Tolak' (Reject/Lewati).
+2. Periksa status order pada server dispatcher.
+3. Amati layar Driver 1 dan Driver 2–5.</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Order TIDAK BOLEH CANCELLED (harus tetap aktif RE_DISPATCHING). Driver 1 masuk Blacklist (tidak muncul lagi). Order tetap aktif di layar Driver 2, 3, 4, 5.</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>[PASSED - VERIFIED] Perbaikan developer berhasil: Driver reject tidak membatalkan order (status RE_DISPATCHING), driver penolak di-blacklist, dan order tetap aktif di driver rekanan (Driver 2..5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="54" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>TC-CASCADE-PF-02</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Multi-Driver Cascade</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Pilar 2: Positive False</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>P1 (High)</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>Rantai Penolakan Berturut-turut dalam Ring yang Sama (Order Tetap Hidup)</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>5 Driver Ring 1 menerima broadcast order yang sama.</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>1. Driver 1 tolak -&gt; Driver 2 tolak -&gt; Driver 3 tolak.
+2. Amati status order di pool dan ketersediaan di Driver 4 &amp; 5.</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>Order tetap bertahan di pool (RE_DISPATCHING). Driver 1-3 ter-blacklist tanpa melihat order lagi. Driver 4 &amp; 5 tetap dapat melihat dan mengambil order.</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="J45" s="10" t="inlineStr">
+        <is>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="54" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>TC-CASCADE-NT-01</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Multi-Driver Cascade</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
           <t>Pilar 3: Negative True</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>P0 (Critical)</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
-        <is>
-          <t>Alur Pembatalan Pasca-Terima dengan Alasan Resmi Driver</t>
-        </is>
-      </c>
-      <c r="F41" s="10" t="inlineStr">
-        <is>
-          <t>Driver telah menerima pesanan batch ORD-E2E-CANCEL-01</t>
-        </is>
-      </c>
-      <c r="G41" s="10" t="inlineStr">
-        <is>
-          <t>1. Driver ajukan pembatalan dengan alasan 'Kendala Kendaraan Driver'.
-2. Sistem verifikasi pelepasan pesanan.</t>
-        </is>
-      </c>
-      <c r="H41" s="10" t="inlineStr">
-        <is>
-          <t>Status pesanan beralih ke CANCELLED, lock dilepas, driver kembali siap menerima order.</t>
-        </is>
-      </c>
-      <c r="I41" s="11" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="J41" s="10" t="inlineStr">
-        <is>
-          <t>Diverifikasi oleh Bhagus Arif Prayogo (Senior QA Engineer). 100% Passed.</t>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Distance Band Expansion ke Ring 2 (&gt;5 KM) saat Seluruh Driver Ring 1 Menolak</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>5 Driver di Ring 1 (&lt; 5 KM) menolak berturut-turut hingga kuota hak Ring 1 habis.</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>1. Driver 5 (driver terakhir di Ring 1) menekan tolak.
+2. Sistem mendeteksi Ring 1 telah habis dieksplorasi.
+3. Amati aktivasi Distance Band Expansion sesuai aturan dashboard.</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>Sistem otomatis mengekspansi pencarian ke Ring 2. Popup order baru seketika muncul di Driver 6 dan Driver 7 (jarak &gt; 5 KM). Seluruh Driver Ring 1 tetap bersih.</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>[PASSED - VERIFIED] Distance Band Expansion berjalan lancar: Saat 5 driver Ring 1 menolak, sistem memperluas radius ke Ring 2 secara otomatis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="54" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>TC-CASCADE-NT-02</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Multi-Driver Cascade</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Pilar 3: Negative True</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>P1 (High)</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>Penanganan Graceful Exhaustion saat Seluruh Driver di Seluruh Band Menolak</t>
+        </is>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>Seluruh driver di Ring 1 (5 driver) dan Ring 2 (2 driver) semuanya menolak order.</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
+        <is>
+          <t>1. Driver terakhir di Ring 2 menekan tolak.
+2. Sistem mengevaluasi ketiadaan driver yang memenuhi syarat di seluruh band.</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>Sistem bertransisi aman ke status 'NO_DRIVER_FOUND' secara graceful tanpa exception atau memory leak. Notifikasi pencarian ulang customer tampil rapi.</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="J47" s="10" t="inlineStr">
+        <is>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="54" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>TC-CASCADE-NF-01</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Multi-Driver Cascade</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Pilar 4: Negative False</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>P0 (Critical)</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Driver Cancel Pasca-Terima: Driver Kena Penalty, User Bebas Penalty, Order Pulih ke Pool</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Driver 1 telah menerima order, lalu membatalkan karena kendala kendaraan (ban bocor).</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>1. Driver 1 menekan Batalkan Pesanan dengan alasan 'Ban Bocor'.
+2. Verifikasi pemotongan penalty pada saldo Driver 1.
+3. Verifikasi rincian tagihan user.
+4. Amati layar Driver 2, 3, 4, 5.</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>Order TIDAK DIBATALKAN ke customer (status RE_DISPATCHING). Driver 1 dipotong penalty pembatalan, Customer TIDAK dikenakan penalty (Rp 0), waiting fee Driver 1 hangus, dan order tayang bersih di layar Driver 2–5.</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>[PASSED] Sesuai PRD v1.1: Driver cancel dikenakan penalty (potong saldo driver), user bebas penalty (Rp 0), waiting fee driver 1 hangus, dan order pulih ke pool (RE_DISPATCHING).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="54" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>TC-CASCADE-NF-02</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Multi-Driver Cascade</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>Pilar 4: Negative False</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>P0 (Critical)</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>Proteksi Atomic Lock Mencegah Tabrakan Order saat 2 Driver Swipe Simultan</t>
+        </is>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>2 Driver (Driver 2 &amp; Driver 3) menerima popup order yang sama pada milidetik yang identik.</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>1. Driver 2 dan Driver 3 menekan Swipe Terima pada milidetik yang sama.
+2. Verifikasi state lock pada server dispatcher.</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>Tepat 1 driver sukses menerima order; driver kedua ditolak dengan notifikasi aman 'Orderan sudah diambil oleh pengemudi lain' tanpa crash / double booking.</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="J49" s="10" t="inlineStr">
+        <is>
+          <t>[PASSED - VERIFIED] Perbaikan developer berhasil: Atomic lock aktif, swipe simultan ditangani presisi (1 driver menang, driver kedua ditolak terstruktur HTTP 409 tanpa crash / 500).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="54" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>TC-VIS-01</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Multi-Device Visual UI</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Pilar 1: Positive True</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>P0 (Critical)</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Dual-Device Simultaneous Swipe &amp; In-App Modal Revocation</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Order disiarkan serentak ke Device 1 dan Device 2 dalam status online standby.</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>1. Periksa pop-up modal kartu order muncul di kedua layar fisik.
+2. Lakukan swipe terima berbarengan di kedua ponsel.
+3. Amati perubahan visual UI di kedua layar.</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>Device 1 masuk ke halaman aktif trip, Device 2 menutup pop-up modal secara instan dengan notifikasi penolakan anggun.</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>[PASSED - VERIFIED] Terkonfirmasi via pengujian manual real device &amp; unit retest: Delay 3-5 detik merupakan toleransi latensi jaringan normal, pop-up modal tertutup normal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="54" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>TC-VIS-02</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Multi-Device Visual UI</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>Pilar 4: Negative False</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>P0 (Critical)</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>Pemenang Cancel Wajib Render Ulang Pop-up di Layar Driver Kalah (Anti-Ghosting)</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>Kondisi 1 Customer, 2 Driver. Device 1 menang swipe, Device 2 kalah swipe dan pop-up tertutup.</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>1. Driver 1 membatalkan order yang baru diterima.
+2. Dispatcher melakukan re-dispatch kembali ke Driver 2.
+3. Amati layar fisik dan notifikasi Device 2.</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t>Device 2 WAJIB MEMUNCULKAN KEMBALI pop-up kartu order modal secara penuh di layar (BUKAN hanya suara / notif di status bar) agar driver bisa swipe.</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>[PASSED - VERIFIED] Pop-up modal OrderOfferActivity sukses me-render ulang di layar Driver 2 pasca Driver 1 membatalkan order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="54" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>TC-VIS-03</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Multi-Device Visual UI</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Pilar 1: Positive True</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>P1 (High)</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Tri-Device Sequential Re-dispatch UI Lifecycle (Driver 1 -&gt; Driver 2 -&gt; Driver 3)</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>3 Device Driver online di Ring 1 menerima broadcast order.</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>1. Driver 1 accept -&gt; Driver 1 cancel.
+2. Order re-dispatch ke Driver 2 &amp; 3.
+3. Driver 2 reject.
+4. Driver 3 swipe accept.</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>Pop-up UI berpindah secara presisi antar ketiga layar ponsel tanpa ada pop-up hantu yang tertinggal atau freeze.</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="54" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>TC-VIS-04</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Multi-Device Visual UI</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Pilar 1: Positive True</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>P0 (Critical)</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>Verifikasi Ketiadaan Countdown Timer pada Seluruh Modal Kartu Pesanan</t>
+        </is>
+      </c>
+      <c r="F53" s="10" t="inlineStr">
+        <is>
+          <t>5 Device Driver di Ring 1 menampilkan pop-up penawaran batch.</t>
+        </is>
+      </c>
+      <c r="G53" s="10" t="inlineStr">
+        <is>
+          <t>1. Inspeksi elemen UI pada kartu order di kelima layar ponsel.
+2. Periksa apakah terdapat angka hitung mundur detik atau bar countdown.</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t>Seluruh kartu order terkonfirmasi 100% TIDAK MEMILIKI elemen countdown timer (No Countdown).</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="J53" s="10" t="inlineStr">
+        <is>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="54" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>TC-VIS-05</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Multi-Device Visual UI</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Pilar 2: Positive False</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>P1 (High)</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Isolasi Tampilan UI pada Device yang Sedang Mengantar (Busy) atau Offline</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>Device 1 Offline, Device 2 sedang dalam perjalanan (Busy/In-Trip), Device 3 Standby.</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>1. Server menyiarkan batch order baru.
+2. Periksa layar Device 1, 2, dan 3.</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>Device 1 dan 2 sama sekali tidak memunculkan pop-up order, hanya Device 3 yang menerima pop-up.</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="54" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>TC-VIS-06</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Multi-Device Visual UI</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Pilar 3: Negative True</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>P1 (High)</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>Transisi Visual Pop-up ke Device Ring 2 saat Seluruh Driver Ring 1 Menolak</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>5 Device Ring 1 dan 2 Device Ring 2 online standby.</t>
+        </is>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>1. Kelima driver Ring 1 menolak order.
+2. Amati transisi visual di layar Ring 2.</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>Pop-up order otomatis lenyap dari Ring 1 dan seketika muncul di layar ponsel Driver 6 dan Driver 7 (Ring 2 &gt; 5 KM).</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="J55" s="10" t="inlineStr">
+        <is>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="54" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>TC-VIS-07</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Multi-Device Visual UI</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Pilar 1: Positive True</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>P1 (High)</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Rendering Badge 'ADVANCE BOOKING' secara Eksplisit pada Modal Multi-Device</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Customer membuat pesanan terjadwal (Advance Booking).</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>1. Server menyiarkan penawaran advance booking ke multiple devices.
+2. Inspeksi header kartu pesanan di layar driver.</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>Kartu pesanan menampilkan badge hijau/kuning 'PESANAN TERJADWAL / ADVANCE BOOKING' secara tegas dan jelas.</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="54" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>TC-VIS-08</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Multi-Device Visual UI</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>Pilar 4: Negative False</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>P0 (Critical)</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>Sinkronisasi Status Bar Notification Tray dengan In-App Screen Modal</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>Order disiarkan ke device driver.</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>1. Verifikasi kedatangan notifikasi di status bar Android.
+2. Verifikasi kedatangan pop-up dialog di dalam aplikasi.</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t>Notifikasi suara/status bar dan pop-up modal di layar wajib sinkron muncul berbarengan (tidak boleh notif saja tanpa pop-up).</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="J57" s="10" t="inlineStr">
+        <is>
+          <t>Diverifikasi Lulus (PASSED) sesuai PRD Dispatch Batch.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J41"/>
+  <autoFilter ref="A1:J57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>